--- a/DataProvider/TestCases_SurfaceUI.xlsx
+++ b/DataProvider/TestCases_SurfaceUI.xlsx
@@ -256,7 +256,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="39.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="77.2"/>
@@ -305,7 +305,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -342,7 +342,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">

--- a/DataProvider/TestCases_SurfaceUI.xlsx
+++ b/DataProvider/TestCases_SurfaceUI.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="11">
   <si>
     <t xml:space="preserve">Test Case ID</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t xml:space="preserve">test_GUI_APP_Branding_Hdfc_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">True</t>
   </si>
 </sst>
 </file>
@@ -256,7 +259,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="39.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="77.2"/>
@@ -316,7 +319,7 @@
         <v>6</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -342,7 +345,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">

--- a/DataProvider/TestCases_SurfaceUI.xlsx
+++ b/DataProvider/TestCases_SurfaceUI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">GUI/APP</t>
   </si>
   <si>
-    <t xml:space="preserve">False</t>
+    <t xml:space="preserve">True</t>
   </si>
   <si>
     <t xml:space="preserve">test_GUI_APP_Branding_Axis_02</t>
@@ -256,7 +256,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="39.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="77.2"/>
@@ -342,7 +342,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">

--- a/DataProvider/TestCases_SurfaceUI.xlsx
+++ b/DataProvider/TestCases_SurfaceUI.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
   <si>
     <t xml:space="preserve">Test Case ID</t>
   </si>
@@ -44,16 +44,13 @@
     <t xml:space="preserve">GUI/APP</t>
   </si>
   <si>
-    <t xml:space="preserve">False</t>
+    <t xml:space="preserve">True</t>
   </si>
   <si>
     <t xml:space="preserve">test_GUI_APP_Branding_Axis_02</t>
   </si>
   <si>
     <t xml:space="preserve">test_GUI_APP_Branding_Hdfc_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">True</t>
   </si>
 </sst>
 </file>
@@ -259,7 +256,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="39.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="77.2"/>
@@ -319,7 +316,7 @@
         <v>6</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -345,7 +342,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">

--- a/DataProvider/TestCases_SurfaceUI.xlsx
+++ b/DataProvider/TestCases_SurfaceUI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">GUI/APP</t>
   </si>
   <si>
-    <t xml:space="preserve">False</t>
+    <t xml:space="preserve">True</t>
   </si>
   <si>
     <t xml:space="preserve">test_GUI_APP_Branding_Axis_02</t>
@@ -256,7 +256,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="39.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="77.2"/>
@@ -342,7 +342,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">

--- a/DataProvider/TestCases_SurfaceUI.xlsx
+++ b/DataProvider/TestCases_SurfaceUI.xlsx
@@ -256,7 +256,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="39.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="77.2"/>
@@ -342,7 +342,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">

--- a/DataProvider/TestCases_SurfaceUI.xlsx
+++ b/DataProvider/TestCases_SurfaceUI.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="11">
   <si>
     <t xml:space="preserve">Test Case ID</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t xml:space="preserve">test_GUI_APP_Branding_Axis_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">False</t>
   </si>
   <si>
     <t xml:space="preserve">test_GUI_APP_Branding_Hdfc_03</t>
@@ -256,7 +259,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="39.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="77.2"/>
@@ -302,12 +305,12 @@
         <v>6</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>5</v>
@@ -316,7 +319,7 @@
         <v>6</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -342,7 +345,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">

--- a/DataProvider/TestCases_SurfaceUI.xlsx
+++ b/DataProvider/TestCases_SurfaceUI.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
   <si>
     <t xml:space="preserve">Test Case ID</t>
   </si>
@@ -44,13 +44,10 @@
     <t xml:space="preserve">GUI/APP</t>
   </si>
   <si>
-    <t xml:space="preserve">True</t>
+    <t xml:space="preserve">False</t>
   </si>
   <si>
     <t xml:space="preserve">test_GUI_APP_Branding_Axis_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">False</t>
   </si>
   <si>
     <t xml:space="preserve">test_GUI_APP_Branding_Hdfc_03</t>
@@ -259,7 +256,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="12.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="39.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="77.2"/>
@@ -305,12 +302,12 @@
         <v>6</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>5</v>
@@ -319,7 +316,7 @@
         <v>6</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -345,7 +342,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="12.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">

--- a/DataProvider/TestCases_SurfaceUI.xlsx
+++ b/DataProvider/TestCases_SurfaceUI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">GUI/APP</t>
   </si>
   <si>
-    <t xml:space="preserve">True</t>
+    <t xml:space="preserve">False</t>
   </si>
   <si>
     <t xml:space="preserve">test_GUI_APP_Branding_Axis_02</t>
@@ -256,7 +256,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="39.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="77.2"/>
@@ -342,7 +342,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">

--- a/DataProvider/TestCases_SurfaceUI.xlsx
+++ b/DataProvider/TestCases_SurfaceUI.xlsx
@@ -5,27 +5,30 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="GUI_APP" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="GUI_Portal" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="10">
   <si>
     <t xml:space="preserve">Test Case ID</t>
   </si>
   <si>
+    <t xml:space="preserve">Sub Feature Code</t>
+  </si>
+  <si>
     <t xml:space="preserve">File Name</t>
   </si>
   <si>
@@ -42,9 +45,6 @@
   </si>
   <si>
     <t xml:space="preserve">GUI/APP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">False</t>
   </si>
   <si>
     <t xml:space="preserve">test_GUI_APP_Branding_Axis_02</t>
@@ -57,14 +57,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="6">
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+  <fonts count="5">
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -85,31 +85,19 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF00627A"/>
-      <name val="JetBrains Mono"/>
-      <family val="3"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4C7DC"/>
-        <bgColor rgb="FFCCCCFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -121,10 +109,10 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="hair"/>
-      <right style="hair"/>
-      <top style="hair"/>
-      <bottom style="hair"/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -153,29 +141,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -187,66 +159,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF00627A"/>
-      <rgbColor rgb="FFB4C7DC"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -255,83 +167,95 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="39.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="77.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="29.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.38"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="0" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="F2" s="0" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="0" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="F3" s="0" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="0" t="s">
         <v>7</v>
       </c>
+      <c r="F4" s="0" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:D4" type="list">
-      <formula1>"True,False"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter/>
   </headerFooter>
 </worksheet>
 </file>
@@ -341,30 +265,40 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B1:F1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.38"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter/>
   </headerFooter>
 </worksheet>
 </file>
--- a/DataProvider/TestCases_SurfaceUI.xlsx
+++ b/DataProvider/TestCases_SurfaceUI.xlsx
@@ -168,12 +168,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="29.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="29.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.38"/>
   </cols>
@@ -266,7 +266,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:F1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.71"/>
@@ -275,7 +275,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.38"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
